--- a/output/宠物用品-20260929_1119-加拿大.xlsx
+++ b/output/宠物用品-20260929_1119-加拿大.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -483,71 +483,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Buzz Box Liners &amp; Truck Accessories</t>
+          <t>Trash Bag Wholesale GmbH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.buzzboxliners.com/</t>
+          <t>https://flatbag-maker.de/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sales@addictivedesertdesigns.com / sales@theaamgroup.com / csbestop@bestop.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+17804869006 / (780) 486-9006 / (855) 233-8992</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>sales@flatbag-maker.de</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>普通客户</t>
+          <t>重点客户</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Truck accessories store · 17323 107 Ave NW, Edmonton, AB T5S 1E5, Canada</t>
+          <t>Trash Bag Wholesale GmbH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[谷歌地图] Litter Box Liners wholesaler @Lyon</t>
+          <t>[手动采集] https://flatbag-maker.de/</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>德国</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maddies Natural Pet Products Ltd.</t>
+          <t>Buzz Box Liners &amp; Truck Accessories</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.maddiespet.com/?utm_source=gbp&amp;utm_medium=organic</t>
+          <t>https://www.buzzboxliners.com/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maddies_serving_the_pet_industry_200@3.png / maddies@maddiespet.com / example@domain.com</t>
+          <t>sales@addictivedesertdesigns.com / sales@theaamgroup.com / csbestop@bestop.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+18772440734 / +1-877-244-0734 / +1-866-299-0967</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>+17804869006 / (780) 486-9006 / (855) 233-8992</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>65</v>
       </c>
@@ -558,7 +551,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wholesaler · 6655 Dennett Pl, Delta, BC V4G 1N4, Canada</t>
+          <t>Truck accessories store · 17323 107 Ave NW, Edmonton, AB T5S 1E5, Canada</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -575,27 +568,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P'tit Père - Lyon 4</t>
+          <t>Maddies Natural Pet Products Ltd.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.ptitpere.fr/</t>
+          <t>https://www.maddiespet.com/?utm_source=gbp&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>support@ptitpere.fr / bonjour@ptitpere.fr</t>
+          <t>maddies_serving_the_pet_industry_200@3.png / maddies@maddiespet.com / example@domain.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33982734977</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>+18772440734 / +1-877-244-0734 / +1-866-299-0967</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -604,7 +596,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pet store · 10 Rue d'Austerlitz, 69004 Lyon, France</t>
+          <t>Wholesaler · 6655 Dennett Pl, Delta, BC V4G 1N4, Canada</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -621,27 +613,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jack et Dolly Lyon</t>
+          <t>联系我们及地址 – PetMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://jacketdolly-lyon.fr/</t>
+          <t>https://www.petmax.ca/pages/locations-contact-us</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact@jacketdolly.fr</t>
+          <t>support@petmax.ca</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+33472707668</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>474.309.6808 / 201.878.8483 / 695.115.8212</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -650,42 +641,36 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pet supply store · à coté d'Imaginarium et en face de Le Relais des Caves, 12 Pl. Jules Guesde, 69007 Lyon, France</t>
+          <t>联系我们及地址 – PetMax</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[谷歌地图] Litter Box Liners wholesaler @Lyon</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>加拿大</t>
+          <t>[手动采集] https://www.petmax.ca/pages/locations-contact-us</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canaldog Montchat</t>
+          <t>P'tit Père - Lyon 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>http://www.canaldog.com/</t>
+          <t>https://www.ptitpere.fr/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact@canaldog.com</t>
+          <t>support@ptitpere.fr / bonjour@ptitpere.fr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+33478544763</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>+33982734977</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>55</v>
       </c>
@@ -696,7 +681,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pet store · 58 Cours Richard-Vitton, 69003 Lyon, France</t>
+          <t>Pet store · 10 Rue d'Austerlitz, 69004 Lyon, France</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -713,25 +698,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Animalis Lyon 4</t>
+          <t>Jack et Dolly Lyon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://magasin.animalis.com/89-animalis-lyon-4?utm_source=gmb</t>
+          <t>https://jacketdolly-lyon.fr/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>example@domain.com / exemple@domaine.fr / contact@animalis.com</t>
+          <t>contact@jacketdolly.fr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+33487349000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>+33472707668</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>55</v>
       </c>
@@ -742,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pet store · 78 Gd Rue de la Croix-Rousse, 69004 Lyon, France</t>
+          <t>Pet supply store · à coté d'Imaginarium et en face de Le Relais des Caves, 12 Pl. Jules Guesde, 69007 Lyon, France</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -759,44 +743,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Canaldog Montchat</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://www.canaldog.com/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>contact@canaldog.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+33478544763</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>普通客户</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pet store · 58 Cours Richard-Vitton, 69003 Lyon, France</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[谷歌地图] Litter Box Liners wholesaler @Lyon</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Animalis Lyon 4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://magasin.animalis.com/89-animalis-lyon-4?utm_source=gmb</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>example@domain.com / exemple@domaine.fr / contact@animalis.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+33487349000</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>普通客户</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pet store · 78 Gd Rue de la Croix-Rousse, 69004 Lyon, France</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[谷歌地图] Litter Box Liners wholesaler @Lyon</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PetSmart Scarborough Pet Store in Scarborough, Ontario | Store #2009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.petsmart.ca/stores/ca/on/scarborough-store2009.html?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google-my-business</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(416) 335-7922 / 888-839-9638</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Visit your local Scarborough PetSmart store for essential pet supplies like food, treats and more from top brands. Our store also offers Grooming, Training, Adoptions and Curbside Pickup. Find us at 12 William Kitchen Drive or call (416) 335-7922 to learn more. Earn PetSmart Treats loyalty points wi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[手动采集] https://www.petsmart.ca/stores/ca/on/scarborough-store2009.html?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google-my-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Canaldog Vaise</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://boutiques.canaldog.com/canaldogboutiques/fr/store/france/auvergne-rhone-alpes/rhone/lyon/vaise/001</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>+33474712404</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
+      <c r="F11" t="n">
         <v>25</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>观察</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Pet supply store · 22 Rue Mouillard, 69009 Lyon, France</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>[谷歌地图] Litter Box Liners wholesaler @Lyon</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>加拿大</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>谷歌客户开发工具</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8000/</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>谷歌客户开发工具</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[手动采集] http://127.0.0.1:8000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://x.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[手动采集] https://x.com</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
